--- a/Result/profitability/1466.xlsx
+++ b/Result/profitability/1466.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06249999999999999</v>
+        <v>-0.03624999999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>8.574999999999999</v>
+        <v>9.078749999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.06124999999999999</v>
+        <v>-0.06999999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>8.237500000000001</v>
+        <v>8.535</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1125</v>
+        <v>-0.10625</v>
       </c>
       <c r="N4" t="n">
-        <v>7.46375</v>
+        <v>7.663749999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         <v>-2.44</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.43625</v>
+        <v>-0.34875</v>
       </c>
       <c r="N5" t="n">
-        <v>4.80125</v>
+        <v>5.845000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,16 +1139,16 @@
         <v>-0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4025</v>
+        <v>-0.345</v>
       </c>
       <c r="N6" t="n">
-        <v>4.640000000000001</v>
+        <v>5.4075</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>0.62</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2925</v>
+        <v>-0.2099999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>5.2475</v>
+        <v>6.95</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1281,13 +1281,13 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0.17</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.21375</v>
+        <v>-0.2099999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>6.51375</v>
+        <v>6.703749999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>0.28</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2</v>
+        <v>-0.1999999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>5.82</v>
@@ -1649,7 +1649,7 @@
         <v>0.59</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.14375</v>
+        <v>-0.1437499999999999</v>
       </c>
       <c r="N10" t="n">
         <v>6.28125</v>
@@ -1776,7 +1776,7 @@
         <v>1.08</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.00874999999999998</v>
+        <v>-0.008749999999999925</v>
       </c>
       <c r="N11" t="n">
         <v>7.05125</v>
@@ -1903,7 +1903,7 @@
         <v>0.77</v>
       </c>
       <c r="M12" t="n">
-        <v>0.105</v>
+        <v>0.1050000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>7.75</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>564</v>
+      </c>
+      <c r="D75" t="n">
+        <v>484</v>
+      </c>
+      <c r="E75" t="n">
+        <v>80</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>19</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>26</v>
+      </c>
+      <c r="K75" t="n">
+        <v>22</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.05499999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.455</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1764705882352942</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.120253164556962</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.350000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.437177280550775</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
